--- a/NuevasNotas/Matutina/Resultados_Auditoria_Notas/Matriz_Marcada_6BM.xlsx
+++ b/NuevasNotas/Matutina/Resultados_Auditoria_Notas/Matriz_Marcada_6BM.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <color indexed="8"/>
@@ -62,10 +62,16 @@
       <sz val="12"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -98,24 +104,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="003B82F6"/>
+        <bgColor rgb="003B82F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E5E7EB"/>
         <bgColor rgb="00E5E7EB"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F3F4F6"/>
-        <bgColor rgb="00F3F4F6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="15">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -301,13 +301,18 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -317,25 +322,25 @@
     <xf numFmtId="49" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -368,18 +373,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -566,9 +568,9 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="20000" dir="5400000">
+            <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="23000" dir="5400000">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
@@ -648,7 +650,7 @@
         </a:effectLst>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -675,10 +677,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Calibri"/>
-            <a:ea typeface="Calibri"/>
-            <a:cs typeface="Calibri"/>
-            <a:sym typeface="Calibri"/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -925,9 +927,9 @@
           <a:round/>
         </a:ln>
         <a:effectLst>
-          <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="20000" dir="5400000">
+          <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="23000" dir="5400000">
             <a:srgbClr val="000000">
-              <a:alpha val="38000"/>
+              <a:alpha val="35000"/>
             </a:srgbClr>
           </a:outerShdw>
         </a:effectLst>
@@ -1205,7 +1207,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1232,10 +1234,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Calibri"/>
-            <a:ea typeface="Calibri"/>
-            <a:cs typeface="Calibri"/>
-            <a:sym typeface="Calibri"/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -1481,13 +1483,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" style="15" min="1" max="1"/>
-    <col width="40" customWidth="1" style="15" min="2" max="2"/>
-    <col width="25" customWidth="1" style="15" min="3" max="3"/>
-    <col width="60" customWidth="1" style="15" min="4" max="4"/>
+    <col width="35" customWidth="1" style="15" min="1" max="1"/>
+    <col width="25" customWidth="1" style="15" min="2" max="2"/>
+    <col width="30" customWidth="1" style="15" min="3" max="3"/>
+    <col width="12" customWidth="1" style="15" min="4" max="4"/>
+    <col width="12" customWidth="1" style="15" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" s="15">
@@ -1499,362 +1502,69 @@
       <c r="B1" s="22" t="n"/>
       <c r="C1" s="22" t="n"/>
       <c r="D1" s="22" t="n"/>
-    </row>
-    <row r="2" ht="20" customHeight="1" s="15">
-      <c r="A2" s="23" t="inlineStr">
-        <is>
-          <t>Curso</t>
-        </is>
-      </c>
-      <c r="B2" s="23" t="inlineStr">
+      <c r="E1" s="22" t="n"/>
+    </row>
+    <row r="3" ht="20" customHeight="1" s="15">
+      <c r="A3" s="23" t="inlineStr">
+        <is>
+          <t>▶ CURSO: 6BM</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1" s="15">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>Estudiante</t>
         </is>
       </c>
-      <c r="C2" s="23" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>Tipo de Problema</t>
         </is>
       </c>
-      <c r="D2" s="23" t="inlineStr">
-        <is>
-          <t>Detalle de la Discrepancia</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1" s="15">
-      <c r="A3" s="24" t="inlineStr">
-        <is>
-          <t>6BM</t>
-        </is>
-      </c>
-      <c r="B3" s="25" t="inlineStr">
-        <is>
-          <t>BUSTAMANTE GUAMINGA DANNA</t>
-        </is>
-      </c>
-      <c r="C3" s="24" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN SISTEMA</t>
-        </is>
-      </c>
-      <c r="D3" s="25" t="inlineStr">
-        <is>
-          <t>El estudiante está en la matriz del docente pero no en el reporte oficial.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="25" customHeight="1" s="15">
-      <c r="A4" s="26" t="inlineStr">
-        <is>
-          <t>6BM</t>
-        </is>
-      </c>
-      <c r="B4" s="27" t="inlineStr">
-        <is>
-          <t>BUSTAMANTE GUAMINGA OANNA YAIDEN</t>
-        </is>
-      </c>
-      <c r="C4" s="26" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN DOCENTE</t>
-        </is>
-      </c>
-      <c r="D4" s="27" t="inlineStr">
-        <is>
-          <t>El estudiante está en el reporte oficial pero falta en la matriz del docente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1" s="15">
-      <c r="A5" s="24" t="inlineStr">
-        <is>
-          <t>6BM</t>
+      <c r="C4" s="24" t="inlineStr">
+        <is>
+          <t>Materia</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>Docente</t>
+        </is>
+      </c>
+      <c r="E4" s="24" t="inlineStr">
+        <is>
+          <t>Sistema</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1" s="15">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>CEREZO CARVAJAL ALAN SANTIAGO</t>
         </is>
       </c>
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>CEREZO CARVAJAL ALAN SANTIAGO</t>
-        </is>
-      </c>
-      <c r="C5" s="24" t="inlineStr">
-        <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
-        <is>
-          <t>Lengua y Literatura (Docente: 8.01 vs Sistema: 8.1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="25" customHeight="1" s="15">
-      <c r="A6" s="26" t="inlineStr">
-        <is>
-          <t>6BM</t>
-        </is>
-      </c>
-      <c r="B6" s="27" t="inlineStr">
-        <is>
-          <t>CHISAGUANO QUINDE FERNANDO FABRICIO</t>
-        </is>
-      </c>
-      <c r="C6" s="26" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN SISTEMA</t>
-        </is>
-      </c>
-      <c r="D6" s="27" t="inlineStr">
-        <is>
-          <t>El estudiante está en la matriz del docente pero no en el reporte oficial.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="25" customHeight="1" s="15">
-      <c r="A7" s="24" t="inlineStr">
-        <is>
-          <t>6BM</t>
-        </is>
-      </c>
-      <c r="B7" s="25" t="inlineStr">
-        <is>
-          <t>CHISAGUANO QUINDI FERNANDO FABRICIO</t>
-        </is>
-      </c>
-      <c r="C7" s="24" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN DOCENTE</t>
-        </is>
-      </c>
-      <c r="D7" s="25" t="inlineStr">
-        <is>
-          <t>El estudiante está en el reporte oficial pero falta en la matriz del docente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="25" customHeight="1" s="15">
-      <c r="A8" s="26" t="inlineStr">
-        <is>
-          <t>6BM</t>
-        </is>
-      </c>
-      <c r="B8" s="27" t="inlineStr">
-        <is>
-          <t>GUIRACOCHA USHCA SNAYDER YAEL</t>
-        </is>
-      </c>
-      <c r="C8" s="26" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D8" s="27" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="25" customHeight="1" s="15">
-      <c r="A9" s="24" t="inlineStr">
-        <is>
-          <t>6BM</t>
-        </is>
-      </c>
-      <c r="B9" s="25" t="inlineStr">
-        <is>
-          <t>INGA IDROVO CRISTIAN ALEXANDER</t>
-        </is>
-      </c>
-      <c r="C9" s="24" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D9" s="25" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="25" customHeight="1" s="15">
-      <c r="A10" s="26" t="inlineStr">
-        <is>
-          <t>6BM</t>
-        </is>
-      </c>
-      <c r="B10" s="27" t="inlineStr">
-        <is>
-          <t>MONAR CARDENAS DYLA SNEYDER</t>
-        </is>
-      </c>
-      <c r="C10" s="26" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN SISTEMA</t>
-        </is>
-      </c>
-      <c r="D10" s="27" t="inlineStr">
-        <is>
-          <t>El estudiante está en la matriz del docente pero no en el reporte oficial.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="25" customHeight="1" s="15">
-      <c r="A11" s="24" t="inlineStr">
-        <is>
-          <t>6BM</t>
-        </is>
-      </c>
-      <c r="B11" s="25" t="inlineStr">
-        <is>
-          <t>MONAR CARDENAS DYLAN SNEYDER</t>
-        </is>
-      </c>
-      <c r="C11" s="24" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN DOCENTE</t>
-        </is>
-      </c>
-      <c r="D11" s="25" t="inlineStr">
-        <is>
-          <t>El estudiante está en el reporte oficial pero falta en la matriz del docente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="25" customHeight="1" s="15">
-      <c r="A12" s="26" t="inlineStr">
-        <is>
-          <t>6BM</t>
-        </is>
-      </c>
-      <c r="B12" s="27" t="inlineStr">
-        <is>
-          <t>RODRIGUEZ JIMBO ASHLEY NICOLE</t>
-        </is>
-      </c>
-      <c r="C12" s="26" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN SISTEMA</t>
-        </is>
-      </c>
-      <c r="D12" s="27" t="inlineStr">
-        <is>
-          <t>El estudiante está en la matriz del docente pero no en el reporte oficial.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="25" customHeight="1" s="15">
-      <c r="A13" s="24" t="inlineStr">
-        <is>
-          <t>6BM</t>
-        </is>
-      </c>
-      <c r="B13" s="25" t="inlineStr">
-        <is>
-          <t>RODRIGUEZ JIMBO ASHLY NICOLE</t>
-        </is>
-      </c>
-      <c r="C13" s="24" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN DOCENTE</t>
-        </is>
-      </c>
-      <c r="D13" s="25" t="inlineStr">
-        <is>
-          <t>El estudiante está en el reporte oficial pero falta en la matriz del docente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="25" customHeight="1" s="15">
-      <c r="A14" s="26" t="inlineStr">
-        <is>
-          <t>6BM</t>
-        </is>
-      </c>
-      <c r="B14" s="27" t="inlineStr">
-        <is>
-          <t>SIMBAÑA GUZHÑAY MADELEINE SIHÁRE</t>
-        </is>
-      </c>
-      <c r="C14" s="26" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D14" s="27" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="25" customHeight="1" s="15">
-      <c r="A15" s="24" t="inlineStr">
-        <is>
-          <t>6BM</t>
-        </is>
-      </c>
-      <c r="B15" s="25" t="inlineStr">
-        <is>
-          <t>SOLIS HUATATOCA ALONDRA MICHAELA</t>
-        </is>
-      </c>
-      <c r="C15" s="24" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D15" s="25" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="25" customHeight="1" s="15">
-      <c r="A16" s="26" t="inlineStr">
-        <is>
-          <t>6BM</t>
-        </is>
-      </c>
-      <c r="B16" s="27" t="inlineStr">
-        <is>
-          <t>VILLA QUIZHPI CARLOS ALEXANDER</t>
-        </is>
-      </c>
-      <c r="C16" s="26" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN SISTEMA</t>
-        </is>
-      </c>
-      <c r="D16" s="27" t="inlineStr">
-        <is>
-          <t>El estudiante está en la matriz del docente pero no en el reporte oficial.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="25" customHeight="1" s="15">
-      <c r="A17" s="24" t="inlineStr">
-        <is>
-          <t>6BM</t>
-        </is>
-      </c>
-      <c r="B17" s="25" t="inlineStr">
-        <is>
-          <t>VILLA QUIZHPI CARLOS ALEXSANDER</t>
-        </is>
-      </c>
-      <c r="C17" s="24" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN DOCENTE</t>
-        </is>
-      </c>
-      <c r="D17" s="25" t="inlineStr">
-        <is>
-          <t>El estudiante está en el reporte oficial pero falta en la matriz del docente.</t>
-        </is>
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t>Lengua y Literatura</t>
+        </is>
+      </c>
+      <c r="D5" s="25" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="E5" s="25" t="n">
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2412,7 +2122,7 @@
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>BUSTAMANTE GUAMINGA DANNA</t>
+          <t>BUSTAMANTE GUAMINGA OANNA</t>
         </is>
       </c>
       <c r="D13" s="13" t="n">
